--- a/StructureDefinition-VunsPneumoComposition.xlsx
+++ b/StructureDefinition-VunsPneumoComposition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22235" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22235" uniqueCount="1281">
   <si>
     <t>Property</t>
   </si>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil pour une Composition Discharge Report en pneumologie dans le cadre du projet Vers Un Souffle Nouveau</t>
+    <t>Profile for Composition as hospital discharge report in the scope of the 'Vers Un Souffle Nouveau' project</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1966,6 +1966,10 @@
     <t>Composition.section:sectionVitalSigns.entry</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/StructureDefinition/VunsPneumoVitalSign)
+</t>
+  </si>
+  <si>
     <t>Composition.section:sectionVitalSigns.emptyReason</t>
   </si>
   <si>
@@ -2275,7 +2279,7 @@
     <t>Composition.section:sectionSignificantProcedures.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/hdr/StructureDefinition/procedure-eu-hdr)
+    <t xml:space="preserve">Reference(http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/StructureDefinition/VunsEfr)
 </t>
   </si>
   <si>
@@ -3289,6 +3293,10 @@
     <t>Composition.section:sectionProceduresHx.entry</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/hdr/StructureDefinition/procedure-eu-hdr)
+</t>
+  </si>
+  <si>
     <t>Patient past procedures pertinent to the scope of this document.</t>
   </si>
   <si>
@@ -3823,6 +3831,10 @@
   </si>
   <si>
     <t>Composition.section:sectionTobaccoUse.entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/StructureDefinition/VunsTobaccoObservation)
+</t>
   </si>
   <si>
     <t>Composition.section:sectionTobaccoUse.emptyReason</t>
@@ -19078,7 +19090,7 @@
         <v>19</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>551</v>
@@ -19169,7 +19181,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>557</v>
@@ -19288,7 +19300,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>565</v>
@@ -19405,13 +19417,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>19</v>
@@ -19436,10 +19448,10 @@
         <v>395</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -19522,7 +19534,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>503</v>
@@ -19637,7 +19649,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>504</v>
@@ -19754,7 +19766,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>505</v>
@@ -19873,7 +19885,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>506</v>
@@ -19992,7 +20004,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>512</v>
@@ -20040,7 +20052,7 @@
         <v>19</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>19</v>
@@ -20111,7 +20123,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>519</v>
@@ -20228,7 +20240,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>523</v>
@@ -20345,7 +20357,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>528</v>
@@ -20462,7 +20474,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>534</v>
@@ -20581,7 +20593,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>542</v>
@@ -20700,7 +20712,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>550</v>
@@ -20817,7 +20829,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>557</v>
@@ -20936,7 +20948,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>565</v>
@@ -21053,13 +21065,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>19</v>
@@ -21084,10 +21096,10 @@
         <v>395</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -21170,7 +21182,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>503</v>
@@ -21285,7 +21297,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>504</v>
@@ -21402,7 +21414,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>505</v>
@@ -21521,7 +21533,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>506</v>
@@ -21640,7 +21652,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>512</v>
@@ -21688,7 +21700,7 @@
         <v>19</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>19</v>
@@ -21759,7 +21771,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>519</v>
@@ -21876,7 +21888,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>523</v>
@@ -21993,7 +22005,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>528</v>
@@ -22110,7 +22122,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>534</v>
@@ -22229,7 +22241,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>542</v>
@@ -22348,7 +22360,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>550</v>
@@ -22374,13 +22386,13 @@
         <v>19</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>553</v>
@@ -22465,7 +22477,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>557</v>
@@ -22584,7 +22596,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>565</v>
@@ -22701,13 +22713,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>19</v>
@@ -22732,10 +22744,10 @@
         <v>395</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -22818,7 +22830,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>503</v>
@@ -22933,7 +22945,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>504</v>
@@ -23050,7 +23062,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>505</v>
@@ -23169,7 +23181,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>506</v>
@@ -23288,7 +23300,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>512</v>
@@ -23336,7 +23348,7 @@
         <v>19</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>19</v>
@@ -23407,7 +23419,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>519</v>
@@ -23524,7 +23536,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>523</v>
@@ -23641,7 +23653,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>528</v>
@@ -23758,7 +23770,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>534</v>
@@ -23877,7 +23889,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>542</v>
@@ -23996,7 +24008,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>550</v>
@@ -24113,7 +24125,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>557</v>
@@ -24232,7 +24244,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>565</v>
@@ -24349,13 +24361,13 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>19</v>
@@ -24380,10 +24392,10 @@
         <v>395</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -24466,7 +24478,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>503</v>
@@ -24581,7 +24593,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>504</v>
@@ -24698,7 +24710,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>505</v>
@@ -24817,7 +24829,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>506</v>
@@ -24936,7 +24948,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>512</v>
@@ -24984,7 +24996,7 @@
         <v>19</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>19</v>
@@ -25055,7 +25067,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>519</v>
@@ -25172,7 +25184,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>523</v>
@@ -25289,7 +25301,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>528</v>
@@ -25406,7 +25418,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>534</v>
@@ -25525,7 +25537,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>542</v>
@@ -25644,7 +25656,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>550</v>
@@ -25670,7 +25682,7 @@
         <v>19</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L181" t="s" s="2">
         <v>551</v>
@@ -25761,7 +25773,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>557</v>
@@ -25880,7 +25892,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>565</v>
@@ -25997,13 +26009,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>19</v>
@@ -26028,10 +26040,10 @@
         <v>395</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -26114,7 +26126,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>503</v>
@@ -26229,7 +26241,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>504</v>
@@ -26346,7 +26358,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>505</v>
@@ -26465,7 +26477,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>506</v>
@@ -26584,7 +26596,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>512</v>
@@ -26632,7 +26644,7 @@
         <v>19</v>
       </c>
       <c r="S189" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="T189" t="s" s="2">
         <v>19</v>
@@ -26703,7 +26715,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>519</v>
@@ -26820,7 +26832,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>523</v>
@@ -26937,7 +26949,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>528</v>
@@ -27054,7 +27066,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>534</v>
@@ -27173,7 +27185,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>542</v>
@@ -27292,7 +27304,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>550</v>
@@ -27318,7 +27330,7 @@
         <v>19</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L195" t="s" s="2">
         <v>551</v>
@@ -27409,7 +27421,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>557</v>
@@ -27528,7 +27540,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>565</v>
@@ -27645,13 +27657,13 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>19</v>
@@ -27676,10 +27688,10 @@
         <v>395</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -27762,7 +27774,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>503</v>
@@ -27877,7 +27889,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>504</v>
@@ -27994,7 +28006,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>505</v>
@@ -28113,7 +28125,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>506</v>
@@ -28232,7 +28244,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>512</v>
@@ -28280,7 +28292,7 @@
         <v>19</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>19</v>
@@ -28351,7 +28363,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>519</v>
@@ -28468,7 +28480,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>523</v>
@@ -28585,7 +28597,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>528</v>
@@ -28702,7 +28714,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>534</v>
@@ -28821,7 +28833,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>542</v>
@@ -28940,7 +28952,7 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>550</v>
@@ -28966,7 +28978,7 @@
         <v>19</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L209" t="s" s="2">
         <v>551</v>
@@ -29057,7 +29069,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>557</v>
@@ -29176,7 +29188,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>565</v>
@@ -29293,13 +29305,13 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D212" t="s" s="2">
         <v>19</v>
@@ -29324,10 +29336,10 @@
         <v>395</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -29410,7 +29422,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>503</v>
@@ -29525,7 +29537,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>504</v>
@@ -29642,7 +29654,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>505</v>
@@ -29761,7 +29773,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>506</v>
@@ -29880,7 +29892,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>512</v>
@@ -29928,7 +29940,7 @@
         <v>19</v>
       </c>
       <c r="S217" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T217" t="s" s="2">
         <v>19</v>
@@ -29999,7 +30011,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>519</v>
@@ -30116,7 +30128,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>523</v>
@@ -30233,7 +30245,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>528</v>
@@ -30350,7 +30362,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>534</v>
@@ -30469,7 +30481,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>542</v>
@@ -30588,7 +30600,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>550</v>
@@ -30614,7 +30626,7 @@
         <v>19</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>551</v>
@@ -30705,7 +30717,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>557</v>
@@ -30824,7 +30836,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>565</v>
@@ -30941,13 +30953,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>19</v>
@@ -30972,10 +30984,10 @@
         <v>395</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -31058,7 +31070,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>503</v>
@@ -31173,7 +31185,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>504</v>
@@ -31290,7 +31302,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>505</v>
@@ -31409,7 +31421,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>506</v>
@@ -31528,7 +31540,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>512</v>
@@ -31576,7 +31588,7 @@
         <v>19</v>
       </c>
       <c r="S231" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="T231" t="s" s="2">
         <v>19</v>
@@ -31647,7 +31659,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>519</v>
@@ -31764,7 +31776,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>523</v>
@@ -31881,7 +31893,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>528</v>
@@ -31998,7 +32010,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>534</v>
@@ -32117,7 +32129,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>542</v>
@@ -32236,7 +32248,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>550</v>
@@ -32262,13 +32274,13 @@
         <v>19</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N237" t="s" s="2">
         <v>553</v>
@@ -32309,7 +32321,7 @@
         <v>19</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -32351,13 +32363,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>19</v>
@@ -32379,13 +32391,13 @@
         <v>19</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N238" t="s" s="2">
         <v>553</v>
@@ -32470,13 +32482,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>19</v>
@@ -32498,13 +32510,13 @@
         <v>19</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>553</v>
@@ -32589,7 +32601,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>557</v>
@@ -32708,7 +32720,7 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>565</v>
@@ -32825,13 +32837,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>19</v>
@@ -32856,10 +32868,10 @@
         <v>395</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -32942,7 +32954,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>503</v>
@@ -33057,7 +33069,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>504</v>
@@ -33174,7 +33186,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>505</v>
@@ -33293,7 +33305,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>506</v>
@@ -33412,7 +33424,7 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>512</v>
@@ -33460,7 +33472,7 @@
         <v>19</v>
       </c>
       <c r="S247" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="T247" t="s" s="2">
         <v>19</v>
@@ -33531,7 +33543,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>519</v>
@@ -33648,7 +33660,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>523</v>
@@ -33765,7 +33777,7 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>528</v>
@@ -33882,7 +33894,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>534</v>
@@ -34001,7 +34013,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>542</v>
@@ -34120,7 +34132,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>550</v>
@@ -34237,7 +34249,7 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>557</v>
@@ -34356,7 +34368,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>565</v>
@@ -34473,13 +34485,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>19</v>
@@ -34504,10 +34516,10 @@
         <v>395</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
@@ -34590,7 +34602,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>503</v>
@@ -34705,7 +34717,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>504</v>
@@ -34822,7 +34834,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>505</v>
@@ -34941,7 +34953,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>506</v>
@@ -35060,7 +35072,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>512</v>
@@ -35108,7 +35120,7 @@
         <v>19</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>19</v>
@@ -35179,7 +35191,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>519</v>
@@ -35296,7 +35308,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>523</v>
@@ -35413,7 +35425,7 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>528</v>
@@ -35530,7 +35542,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>534</v>
@@ -35649,7 +35661,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>542</v>
@@ -35768,7 +35780,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>550</v>
@@ -35794,7 +35806,7 @@
         <v>19</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L267" t="s" s="2">
         <v>551</v>
@@ -35885,7 +35897,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>557</v>
@@ -36004,7 +36016,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>565</v>
@@ -36121,13 +36133,13 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D270" t="s" s="2">
         <v>19</v>
@@ -36152,10 +36164,10 @@
         <v>395</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" s="2"/>
@@ -36238,7 +36250,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>503</v>
@@ -36353,7 +36365,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>504</v>
@@ -36470,7 +36482,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>505</v>
@@ -36589,7 +36601,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>506</v>
@@ -36708,7 +36720,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>512</v>
@@ -36756,7 +36768,7 @@
         <v>19</v>
       </c>
       <c r="S275" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="T275" t="s" s="2">
         <v>19</v>
@@ -36827,7 +36839,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>519</v>
@@ -36944,7 +36956,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>523</v>
@@ -37061,7 +37073,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>528</v>
@@ -37178,7 +37190,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>534</v>
@@ -37297,7 +37309,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>542</v>
@@ -37416,7 +37428,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>550</v>
@@ -37533,7 +37545,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>557</v>
@@ -37652,7 +37664,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>565</v>
@@ -37769,13 +37781,13 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D284" t="s" s="2">
         <v>19</v>
@@ -37800,10 +37812,10 @@
         <v>395</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -37886,7 +37898,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>503</v>
@@ -38001,7 +38013,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>504</v>
@@ -38118,7 +38130,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>505</v>
@@ -38237,7 +38249,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>506</v>
@@ -38356,7 +38368,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>512</v>
@@ -38404,7 +38416,7 @@
         <v>19</v>
       </c>
       <c r="S289" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T289" t="s" s="2">
         <v>19</v>
@@ -38475,7 +38487,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>519</v>
@@ -38592,7 +38604,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>523</v>
@@ -38709,7 +38721,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>528</v>
@@ -38826,7 +38838,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>534</v>
@@ -38945,7 +38957,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>542</v>
@@ -39064,7 +39076,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>550</v>
@@ -39090,7 +39102,7 @@
         <v>19</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L295" t="s" s="2">
         <v>551</v>
@@ -39181,7 +39193,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>557</v>
@@ -39300,7 +39312,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>565</v>
@@ -39417,13 +39429,13 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D298" t="s" s="2">
         <v>19</v>
@@ -39448,10 +39460,10 @@
         <v>395</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="N298" s="2"/>
       <c r="O298" s="2"/>
@@ -39534,7 +39546,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>503</v>
@@ -39649,7 +39661,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>504</v>
@@ -39766,7 +39778,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>505</v>
@@ -39885,7 +39897,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>506</v>
@@ -40004,7 +40016,7 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>512</v>
@@ -40052,7 +40064,7 @@
         <v>19</v>
       </c>
       <c r="S303" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="T303" t="s" s="2">
         <v>19</v>
@@ -40123,7 +40135,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>519</v>
@@ -40240,7 +40252,7 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>523</v>
@@ -40357,7 +40369,7 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>528</v>
@@ -40474,7 +40486,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>534</v>
@@ -40593,7 +40605,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>542</v>
@@ -40712,7 +40724,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>550</v>
@@ -40738,13 +40750,13 @@
         <v>19</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N309" t="s" s="2">
         <v>553</v>
@@ -40785,7 +40797,7 @@
         <v>19</v>
       </c>
       <c r="AB309" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AC309" s="2"/>
       <c r="AD309" t="s" s="2">
@@ -40827,13 +40839,13 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D310" t="s" s="2">
         <v>19</v>
@@ -40855,13 +40867,13 @@
         <v>19</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="N310" t="s" s="2">
         <v>553</v>
@@ -40946,7 +40958,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>557</v>
@@ -41065,7 +41077,7 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>565</v>
@@ -41182,13 +41194,13 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D313" t="s" s="2">
         <v>19</v>
@@ -41213,10 +41225,10 @@
         <v>395</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N313" s="2"/>
       <c r="O313" s="2"/>
@@ -41299,7 +41311,7 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>503</v>
@@ -41414,7 +41426,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>504</v>
@@ -41531,7 +41543,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>505</v>
@@ -41650,7 +41662,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>506</v>
@@ -41769,7 +41781,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>512</v>
@@ -41817,7 +41829,7 @@
         <v>19</v>
       </c>
       <c r="S318" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="T318" t="s" s="2">
         <v>19</v>
@@ -41888,7 +41900,7 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>519</v>
@@ -42005,7 +42017,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>523</v>
@@ -42122,7 +42134,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>528</v>
@@ -42239,7 +42251,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>534</v>
@@ -42358,7 +42370,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>542</v>
@@ -42477,7 +42489,7 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>550</v>
@@ -42506,10 +42518,10 @@
         <v>491</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N324" t="s" s="2">
         <v>553</v>
@@ -42550,7 +42562,7 @@
         <v>19</v>
       </c>
       <c r="AB324" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AC324" s="2"/>
       <c r="AD324" t="s" s="2">
@@ -42592,13 +42604,13 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D325" t="s" s="2">
         <v>19</v>
@@ -42620,13 +42632,13 @@
         <v>19</v>
       </c>
       <c r="K325" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N325" t="s" s="2">
         <v>553</v>
@@ -42711,7 +42723,7 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>557</v>
@@ -42830,7 +42842,7 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>565</v>
@@ -42947,13 +42959,13 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D328" t="s" s="2">
         <v>19</v>
@@ -42978,10 +42990,10 @@
         <v>395</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="N328" s="2"/>
       <c r="O328" s="2"/>
@@ -43064,7 +43076,7 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>503</v>
@@ -43179,7 +43191,7 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>504</v>
@@ -43296,7 +43308,7 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>505</v>
@@ -43415,7 +43427,7 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>506</v>
@@ -43534,7 +43546,7 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>512</v>
@@ -43582,7 +43594,7 @@
         <v>19</v>
       </c>
       <c r="S333" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="T333" t="s" s="2">
         <v>19</v>
@@ -43653,7 +43665,7 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>519</v>
@@ -43770,7 +43782,7 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>523</v>
@@ -43887,7 +43899,7 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>528</v>
@@ -44004,7 +44016,7 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>534</v>
@@ -44123,7 +44135,7 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>542</v>
@@ -44242,7 +44254,7 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>550</v>
@@ -44268,7 +44280,7 @@
         <v>19</v>
       </c>
       <c r="K339" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="L339" t="s" s="2">
         <v>551</v>
@@ -44359,7 +44371,7 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>557</v>
@@ -44478,7 +44490,7 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>565</v>
@@ -44595,13 +44607,13 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D342" t="s" s="2">
         <v>19</v>
@@ -44626,10 +44638,10 @@
         <v>395</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="N342" s="2"/>
       <c r="O342" s="2"/>
@@ -44712,7 +44724,7 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>503</v>
@@ -44827,7 +44839,7 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>504</v>
@@ -44944,7 +44956,7 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>505</v>
@@ -45063,7 +45075,7 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>506</v>
@@ -45182,7 +45194,7 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>512</v>
@@ -45230,7 +45242,7 @@
         <v>19</v>
       </c>
       <c r="S347" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="T347" t="s" s="2">
         <v>19</v>
@@ -45301,7 +45313,7 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>519</v>
@@ -45418,7 +45430,7 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>523</v>
@@ -45535,7 +45547,7 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>528</v>
@@ -45652,7 +45664,7 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>534</v>
@@ -45771,7 +45783,7 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>542</v>
@@ -45890,7 +45902,7 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>550</v>
@@ -46007,7 +46019,7 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>557</v>
@@ -46126,7 +46138,7 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>565</v>
@@ -46243,13 +46255,13 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D356" t="s" s="2">
         <v>19</v>
@@ -46274,10 +46286,10 @@
         <v>395</v>
       </c>
       <c r="L356" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="N356" s="2"/>
       <c r="O356" s="2"/>
@@ -46360,7 +46372,7 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>503</v>
@@ -46475,7 +46487,7 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>504</v>
@@ -46592,7 +46604,7 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>505</v>
@@ -46711,7 +46723,7 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>506</v>
@@ -46830,7 +46842,7 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>512</v>
@@ -46878,7 +46890,7 @@
         <v>19</v>
       </c>
       <c r="S361" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="T361" t="s" s="2">
         <v>19</v>
@@ -46949,7 +46961,7 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>519</v>
@@ -47066,7 +47078,7 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>523</v>
@@ -47183,7 +47195,7 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>528</v>
@@ -47300,7 +47312,7 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>534</v>
@@ -47419,7 +47431,7 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>542</v>
@@ -47538,7 +47550,7 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>550</v>
@@ -47564,13 +47576,13 @@
         <v>19</v>
       </c>
       <c r="K367" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L367" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="N367" t="s" s="2">
         <v>553</v>
@@ -47655,7 +47667,7 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>557</v>
@@ -47774,7 +47786,7 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>565</v>
@@ -47891,13 +47903,13 @@
     </row>
     <row r="370" hidden="true">
       <c r="A370" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D370" t="s" s="2">
         <v>19</v>
@@ -47922,10 +47934,10 @@
         <v>395</v>
       </c>
       <c r="L370" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
@@ -48008,7 +48020,7 @@
     </row>
     <row r="371" hidden="true">
       <c r="A371" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>503</v>
@@ -48123,7 +48135,7 @@
     </row>
     <row r="372" hidden="true">
       <c r="A372" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>504</v>
@@ -48240,7 +48252,7 @@
     </row>
     <row r="373" hidden="true">
       <c r="A373" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>505</v>
@@ -48359,7 +48371,7 @@
     </row>
     <row r="374" hidden="true">
       <c r="A374" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>506</v>
@@ -48478,7 +48490,7 @@
     </row>
     <row r="375" hidden="true">
       <c r="A375" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>512</v>
@@ -48526,7 +48538,7 @@
         <v>19</v>
       </c>
       <c r="S375" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="T375" t="s" s="2">
         <v>19</v>
@@ -48597,7 +48609,7 @@
     </row>
     <row r="376" hidden="true">
       <c r="A376" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>519</v>
@@ -48714,7 +48726,7 @@
     </row>
     <row r="377" hidden="true">
       <c r="A377" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>523</v>
@@ -48831,7 +48843,7 @@
     </row>
     <row r="378" hidden="true">
       <c r="A378" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>528</v>
@@ -48948,7 +48960,7 @@
     </row>
     <row r="379" hidden="true">
       <c r="A379" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>534</v>
@@ -49067,7 +49079,7 @@
     </row>
     <row r="380" hidden="true">
       <c r="A380" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>542</v>
@@ -49186,7 +49198,7 @@
     </row>
     <row r="381" hidden="true">
       <c r="A381" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>550</v>
@@ -49212,13 +49224,13 @@
         <v>19</v>
       </c>
       <c r="K381" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L381" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="N381" t="s" s="2">
         <v>553</v>
@@ -49303,7 +49315,7 @@
     </row>
     <row r="382" hidden="true">
       <c r="A382" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>557</v>
@@ -49422,7 +49434,7 @@
     </row>
     <row r="383" hidden="true">
       <c r="A383" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>565</v>
@@ -49539,13 +49551,13 @@
     </row>
     <row r="384" hidden="true">
       <c r="A384" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D384" t="s" s="2">
         <v>19</v>
@@ -49570,10 +49582,10 @@
         <v>395</v>
       </c>
       <c r="L384" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="N384" s="2"/>
       <c r="O384" s="2"/>
@@ -49656,7 +49668,7 @@
     </row>
     <row r="385" hidden="true">
       <c r="A385" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>503</v>
@@ -49771,7 +49783,7 @@
     </row>
     <row r="386" hidden="true">
       <c r="A386" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>504</v>
@@ -49888,7 +49900,7 @@
     </row>
     <row r="387" hidden="true">
       <c r="A387" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>505</v>
@@ -50007,7 +50019,7 @@
     </row>
     <row r="388" hidden="true">
       <c r="A388" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>506</v>
@@ -50126,7 +50138,7 @@
     </row>
     <row r="389" hidden="true">
       <c r="A389" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>512</v>
@@ -50174,7 +50186,7 @@
         <v>19</v>
       </c>
       <c r="S389" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="T389" t="s" s="2">
         <v>19</v>
@@ -50245,7 +50257,7 @@
     </row>
     <row r="390" hidden="true">
       <c r="A390" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>519</v>
@@ -50362,7 +50374,7 @@
     </row>
     <row r="391" hidden="true">
       <c r="A391" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>523</v>
@@ -50479,7 +50491,7 @@
     </row>
     <row r="392" hidden="true">
       <c r="A392" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>528</v>
@@ -50596,7 +50608,7 @@
     </row>
     <row r="393" hidden="true">
       <c r="A393" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>534</v>
@@ -50715,7 +50727,7 @@
     </row>
     <row r="394" hidden="true">
       <c r="A394" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>542</v>
@@ -50834,7 +50846,7 @@
     </row>
     <row r="395" hidden="true">
       <c r="A395" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>550</v>
@@ -50860,7 +50872,7 @@
         <v>19</v>
       </c>
       <c r="K395" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L395" t="s" s="2">
         <v>551</v>
@@ -50951,7 +50963,7 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>557</v>
@@ -51070,7 +51082,7 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>565</v>
@@ -51187,13 +51199,13 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D398" t="s" s="2">
         <v>19</v>
@@ -51218,10 +51230,10 @@
         <v>395</v>
       </c>
       <c r="L398" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="N398" s="2"/>
       <c r="O398" s="2"/>
@@ -51304,7 +51316,7 @@
     </row>
     <row r="399" hidden="true">
       <c r="A399" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>503</v>
@@ -51419,7 +51431,7 @@
     </row>
     <row r="400" hidden="true">
       <c r="A400" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>504</v>
@@ -51536,7 +51548,7 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>505</v>
@@ -51655,7 +51667,7 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>506</v>
@@ -51774,7 +51786,7 @@
     </row>
     <row r="403" hidden="true">
       <c r="A403" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>512</v>
@@ -51822,7 +51834,7 @@
         <v>19</v>
       </c>
       <c r="S403" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="T403" t="s" s="2">
         <v>19</v>
@@ -51893,7 +51905,7 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>519</v>
@@ -52010,7 +52022,7 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>523</v>
@@ -52127,7 +52139,7 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>528</v>
@@ -52244,7 +52256,7 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>534</v>
@@ -52363,7 +52375,7 @@
     </row>
     <row r="408" hidden="true">
       <c r="A408" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>542</v>
@@ -52482,7 +52494,7 @@
     </row>
     <row r="409" hidden="true">
       <c r="A409" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>550</v>
@@ -52508,13 +52520,13 @@
         <v>19</v>
       </c>
       <c r="K409" t="s" s="2">
-        <v>716</v>
+        <v>1019</v>
       </c>
       <c r="L409" t="s" s="2">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="N409" t="s" s="2">
         <v>553</v>
@@ -52599,7 +52611,7 @@
     </row>
     <row r="410" hidden="true">
       <c r="A410" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>557</v>
@@ -52718,7 +52730,7 @@
     </row>
     <row r="411" hidden="true">
       <c r="A411" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>565</v>
@@ -52835,13 +52847,13 @@
     </row>
     <row r="412" hidden="true">
       <c r="A412" t="s" s="2">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D412" t="s" s="2">
         <v>19</v>
@@ -52866,10 +52878,10 @@
         <v>395</v>
       </c>
       <c r="L412" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="N412" s="2"/>
       <c r="O412" s="2"/>
@@ -52952,7 +52964,7 @@
     </row>
     <row r="413" hidden="true">
       <c r="A413" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>503</v>
@@ -53067,7 +53079,7 @@
     </row>
     <row r="414" hidden="true">
       <c r="A414" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>504</v>
@@ -53184,7 +53196,7 @@
     </row>
     <row r="415" hidden="true">
       <c r="A415" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>505</v>
@@ -53303,7 +53315,7 @@
     </row>
     <row r="416" hidden="true">
       <c r="A416" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>506</v>
@@ -53422,7 +53434,7 @@
     </row>
     <row r="417" hidden="true">
       <c r="A417" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>512</v>
@@ -53470,7 +53482,7 @@
         <v>19</v>
       </c>
       <c r="S417" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="T417" t="s" s="2">
         <v>19</v>
@@ -53541,7 +53553,7 @@
     </row>
     <row r="418" hidden="true">
       <c r="A418" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>519</v>
@@ -53658,7 +53670,7 @@
     </row>
     <row r="419" hidden="true">
       <c r="A419" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>523</v>
@@ -53775,7 +53787,7 @@
     </row>
     <row r="420" hidden="true">
       <c r="A420" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>528</v>
@@ -53892,7 +53904,7 @@
     </row>
     <row r="421" hidden="true">
       <c r="A421" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>534</v>
@@ -54011,7 +54023,7 @@
     </row>
     <row r="422" hidden="true">
       <c r="A422" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>542</v>
@@ -54130,7 +54142,7 @@
     </row>
     <row r="423" hidden="true">
       <c r="A423" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>550</v>
@@ -54156,7 +54168,7 @@
         <v>19</v>
       </c>
       <c r="K423" t="s" s="2">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="L423" t="s" s="2">
         <v>551</v>
@@ -54247,7 +54259,7 @@
     </row>
     <row r="424" hidden="true">
       <c r="A424" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>557</v>
@@ -54366,7 +54378,7 @@
     </row>
     <row r="425" hidden="true">
       <c r="A425" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>565</v>
@@ -54483,13 +54495,13 @@
     </row>
     <row r="426" hidden="true">
       <c r="A426" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D426" t="s" s="2">
         <v>19</v>
@@ -54514,10 +54526,10 @@
         <v>395</v>
       </c>
       <c r="L426" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="N426" s="2"/>
       <c r="O426" s="2"/>
@@ -54600,7 +54612,7 @@
     </row>
     <row r="427" hidden="true">
       <c r="A427" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>503</v>
@@ -54715,7 +54727,7 @@
     </row>
     <row r="428" hidden="true">
       <c r="A428" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B428" t="s" s="2">
         <v>504</v>
@@ -54832,7 +54844,7 @@
     </row>
     <row r="429" hidden="true">
       <c r="A429" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B429" t="s" s="2">
         <v>505</v>
@@ -54951,7 +54963,7 @@
     </row>
     <row r="430" hidden="true">
       <c r="A430" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B430" t="s" s="2">
         <v>506</v>
@@ -55070,7 +55082,7 @@
     </row>
     <row r="431" hidden="true">
       <c r="A431" t="s" s="2">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B431" t="s" s="2">
         <v>512</v>
@@ -55118,7 +55130,7 @@
         <v>19</v>
       </c>
       <c r="S431" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="T431" t="s" s="2">
         <v>19</v>
@@ -55189,7 +55201,7 @@
     </row>
     <row r="432" hidden="true">
       <c r="A432" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B432" t="s" s="2">
         <v>519</v>
@@ -55306,7 +55318,7 @@
     </row>
     <row r="433" hidden="true">
       <c r="A433" t="s" s="2">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B433" t="s" s="2">
         <v>523</v>
@@ -55423,7 +55435,7 @@
     </row>
     <row r="434" hidden="true">
       <c r="A434" t="s" s="2">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B434" t="s" s="2">
         <v>528</v>
@@ -55540,7 +55552,7 @@
     </row>
     <row r="435" hidden="true">
       <c r="A435" t="s" s="2">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B435" t="s" s="2">
         <v>534</v>
@@ -55659,7 +55671,7 @@
     </row>
     <row r="436" hidden="true">
       <c r="A436" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B436" t="s" s="2">
         <v>542</v>
@@ -55778,7 +55790,7 @@
     </row>
     <row r="437" hidden="true">
       <c r="A437" t="s" s="2">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B437" t="s" s="2">
         <v>550</v>
@@ -55804,13 +55816,13 @@
         <v>19</v>
       </c>
       <c r="K437" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="L437" t="s" s="2">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="M437" t="s" s="2">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="N437" t="s" s="2">
         <v>553</v>
@@ -55895,7 +55907,7 @@
     </row>
     <row r="438" hidden="true">
       <c r="A438" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B438" t="s" s="2">
         <v>557</v>
@@ -56014,7 +56026,7 @@
     </row>
     <row r="439" hidden="true">
       <c r="A439" t="s" s="2">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B439" t="s" s="2">
         <v>565</v>
@@ -56131,13 +56143,13 @@
     </row>
     <row r="440" hidden="true">
       <c r="A440" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B440" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D440" t="s" s="2">
         <v>19</v>
@@ -56162,10 +56174,10 @@
         <v>395</v>
       </c>
       <c r="L440" t="s" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="M440" t="s" s="2">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="N440" s="2"/>
       <c r="O440" s="2"/>
@@ -56248,7 +56260,7 @@
     </row>
     <row r="441" hidden="true">
       <c r="A441" t="s" s="2">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B441" t="s" s="2">
         <v>503</v>
@@ -56363,7 +56375,7 @@
     </row>
     <row r="442" hidden="true">
       <c r="A442" t="s" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B442" t="s" s="2">
         <v>504</v>
@@ -56480,7 +56492,7 @@
     </row>
     <row r="443" hidden="true">
       <c r="A443" t="s" s="2">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B443" t="s" s="2">
         <v>505</v>
@@ -56599,7 +56611,7 @@
     </row>
     <row r="444" hidden="true">
       <c r="A444" t="s" s="2">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B444" t="s" s="2">
         <v>506</v>
@@ -56718,7 +56730,7 @@
     </row>
     <row r="445" hidden="true">
       <c r="A445" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B445" t="s" s="2">
         <v>512</v>
@@ -56766,7 +56778,7 @@
         <v>19</v>
       </c>
       <c r="S445" t="s" s="2">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="T445" t="s" s="2">
         <v>19</v>
@@ -56837,7 +56849,7 @@
     </row>
     <row r="446" hidden="true">
       <c r="A446" t="s" s="2">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B446" t="s" s="2">
         <v>519</v>
@@ -56954,7 +56966,7 @@
     </row>
     <row r="447" hidden="true">
       <c r="A447" t="s" s="2">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B447" t="s" s="2">
         <v>523</v>
@@ -57071,7 +57083,7 @@
     </row>
     <row r="448" hidden="true">
       <c r="A448" t="s" s="2">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B448" t="s" s="2">
         <v>528</v>
@@ -57188,7 +57200,7 @@
     </row>
     <row r="449" hidden="true">
       <c r="A449" t="s" s="2">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B449" t="s" s="2">
         <v>534</v>
@@ -57307,7 +57319,7 @@
     </row>
     <row r="450" hidden="true">
       <c r="A450" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B450" t="s" s="2">
         <v>542</v>
@@ -57426,7 +57438,7 @@
     </row>
     <row r="451" hidden="true">
       <c r="A451" t="s" s="2">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B451" t="s" s="2">
         <v>550</v>
@@ -57452,7 +57464,7 @@
         <v>19</v>
       </c>
       <c r="K451" t="s" s="2">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L451" t="s" s="2">
         <v>551</v>
@@ -57543,7 +57555,7 @@
     </row>
     <row r="452" hidden="true">
       <c r="A452" t="s" s="2">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B452" t="s" s="2">
         <v>557</v>
@@ -57662,7 +57674,7 @@
     </row>
     <row r="453" hidden="true">
       <c r="A453" t="s" s="2">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B453" t="s" s="2">
         <v>565</v>
@@ -57779,13 +57791,13 @@
     </row>
     <row r="454" hidden="true">
       <c r="A454" t="s" s="2">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B454" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D454" t="s" s="2">
         <v>19</v>
@@ -57810,10 +57822,10 @@
         <v>395</v>
       </c>
       <c r="L454" t="s" s="2">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="M454" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="N454" s="2"/>
       <c r="O454" s="2"/>
@@ -57896,7 +57908,7 @@
     </row>
     <row r="455" hidden="true">
       <c r="A455" t="s" s="2">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B455" t="s" s="2">
         <v>503</v>
@@ -58011,7 +58023,7 @@
     </row>
     <row r="456" hidden="true">
       <c r="A456" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B456" t="s" s="2">
         <v>504</v>
@@ -58128,7 +58140,7 @@
     </row>
     <row r="457" hidden="true">
       <c r="A457" t="s" s="2">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B457" t="s" s="2">
         <v>505</v>
@@ -58247,7 +58259,7 @@
     </row>
     <row r="458" hidden="true">
       <c r="A458" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B458" t="s" s="2">
         <v>506</v>
@@ -58366,7 +58378,7 @@
     </row>
     <row r="459" hidden="true">
       <c r="A459" t="s" s="2">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B459" t="s" s="2">
         <v>512</v>
@@ -58414,7 +58426,7 @@
         <v>19</v>
       </c>
       <c r="S459" t="s" s="2">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="T459" t="s" s="2">
         <v>19</v>
@@ -58485,7 +58497,7 @@
     </row>
     <row r="460" hidden="true">
       <c r="A460" t="s" s="2">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B460" t="s" s="2">
         <v>519</v>
@@ -58602,7 +58614,7 @@
     </row>
     <row r="461" hidden="true">
       <c r="A461" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B461" t="s" s="2">
         <v>523</v>
@@ -58719,7 +58731,7 @@
     </row>
     <row r="462" hidden="true">
       <c r="A462" t="s" s="2">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B462" t="s" s="2">
         <v>528</v>
@@ -58836,7 +58848,7 @@
     </row>
     <row r="463" hidden="true">
       <c r="A463" t="s" s="2">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B463" t="s" s="2">
         <v>534</v>
@@ -58955,7 +58967,7 @@
     </row>
     <row r="464" hidden="true">
       <c r="A464" t="s" s="2">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B464" t="s" s="2">
         <v>542</v>
@@ -59074,7 +59086,7 @@
     </row>
     <row r="465" hidden="true">
       <c r="A465" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B465" t="s" s="2">
         <v>550</v>
@@ -59100,13 +59112,13 @@
         <v>19</v>
       </c>
       <c r="K465" t="s" s="2">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="L465" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="N465" t="s" s="2">
         <v>553</v>
@@ -59191,7 +59203,7 @@
     </row>
     <row r="466" hidden="true">
       <c r="A466" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B466" t="s" s="2">
         <v>557</v>
@@ -59310,7 +59322,7 @@
     </row>
     <row r="467" hidden="true">
       <c r="A467" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B467" t="s" s="2">
         <v>565</v>
@@ -59427,13 +59439,13 @@
     </row>
     <row r="468" hidden="true">
       <c r="A468" t="s" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B468" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D468" t="s" s="2">
         <v>19</v>
@@ -59458,10 +59470,10 @@
         <v>395</v>
       </c>
       <c r="L468" t="s" s="2">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="N468" s="2"/>
       <c r="O468" s="2"/>
@@ -59544,7 +59556,7 @@
     </row>
     <row r="469" hidden="true">
       <c r="A469" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B469" t="s" s="2">
         <v>503</v>
@@ -59659,7 +59671,7 @@
     </row>
     <row r="470" hidden="true">
       <c r="A470" t="s" s="2">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B470" t="s" s="2">
         <v>504</v>
@@ -59776,7 +59788,7 @@
     </row>
     <row r="471" hidden="true">
       <c r="A471" t="s" s="2">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B471" t="s" s="2">
         <v>505</v>
@@ -59895,7 +59907,7 @@
     </row>
     <row r="472" hidden="true">
       <c r="A472" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B472" t="s" s="2">
         <v>506</v>
@@ -60014,7 +60026,7 @@
     </row>
     <row r="473" hidden="true">
       <c r="A473" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B473" t="s" s="2">
         <v>512</v>
@@ -60062,7 +60074,7 @@
         <v>19</v>
       </c>
       <c r="S473" t="s" s="2">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="T473" t="s" s="2">
         <v>19</v>
@@ -60133,7 +60145,7 @@
     </row>
     <row r="474" hidden="true">
       <c r="A474" t="s" s="2">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B474" t="s" s="2">
         <v>519</v>
@@ -60250,7 +60262,7 @@
     </row>
     <row r="475" hidden="true">
       <c r="A475" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B475" t="s" s="2">
         <v>523</v>
@@ -60367,7 +60379,7 @@
     </row>
     <row r="476" hidden="true">
       <c r="A476" t="s" s="2">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B476" t="s" s="2">
         <v>528</v>
@@ -60484,7 +60496,7 @@
     </row>
     <row r="477" hidden="true">
       <c r="A477" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B477" t="s" s="2">
         <v>534</v>
@@ -60603,7 +60615,7 @@
     </row>
     <row r="478" hidden="true">
       <c r="A478" t="s" s="2">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B478" t="s" s="2">
         <v>542</v>
@@ -60722,7 +60734,7 @@
     </row>
     <row r="479" hidden="true">
       <c r="A479" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B479" t="s" s="2">
         <v>550</v>
@@ -60748,13 +60760,13 @@
         <v>19</v>
       </c>
       <c r="K479" t="s" s="2">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="N479" t="s" s="2">
         <v>553</v>
@@ -60795,7 +60807,7 @@
         <v>19</v>
       </c>
       <c r="AB479" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AC479" s="2"/>
       <c r="AD479" t="s" s="2">
@@ -60837,13 +60849,13 @@
     </row>
     <row r="480" hidden="true">
       <c r="A480" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B480" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="D480" t="s" s="2">
         <v>19</v>
@@ -60865,13 +60877,13 @@
         <v>19</v>
       </c>
       <c r="K480" t="s" s="2">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="N480" t="s" s="2">
         <v>553</v>
@@ -60956,7 +60968,7 @@
     </row>
     <row r="481" hidden="true">
       <c r="A481" t="s" s="2">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B481" t="s" s="2">
         <v>557</v>
@@ -61075,7 +61087,7 @@
     </row>
     <row r="482" hidden="true">
       <c r="A482" t="s" s="2">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B482" t="s" s="2">
         <v>565</v>
@@ -61192,13 +61204,13 @@
     </row>
     <row r="483" hidden="true">
       <c r="A483" t="s" s="2">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B483" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D483" t="s" s="2">
         <v>19</v>
@@ -61223,10 +61235,10 @@
         <v>395</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="N483" s="2"/>
       <c r="O483" s="2"/>
@@ -61309,7 +61321,7 @@
     </row>
     <row r="484" hidden="true">
       <c r="A484" t="s" s="2">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B484" t="s" s="2">
         <v>503</v>
@@ -61424,7 +61436,7 @@
     </row>
     <row r="485" hidden="true">
       <c r="A485" t="s" s="2">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B485" t="s" s="2">
         <v>504</v>
@@ -61541,7 +61553,7 @@
     </row>
     <row r="486" hidden="true">
       <c r="A486" t="s" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B486" t="s" s="2">
         <v>505</v>
@@ -61660,7 +61672,7 @@
     </row>
     <row r="487" hidden="true">
       <c r="A487" t="s" s="2">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B487" t="s" s="2">
         <v>506</v>
@@ -61779,7 +61791,7 @@
     </row>
     <row r="488" hidden="true">
       <c r="A488" t="s" s="2">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B488" t="s" s="2">
         <v>512</v>
@@ -61827,7 +61839,7 @@
         <v>19</v>
       </c>
       <c r="S488" t="s" s="2">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="T488" t="s" s="2">
         <v>19</v>
@@ -61898,7 +61910,7 @@
     </row>
     <row r="489" hidden="true">
       <c r="A489" t="s" s="2">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B489" t="s" s="2">
         <v>519</v>
@@ -62015,7 +62027,7 @@
     </row>
     <row r="490" hidden="true">
       <c r="A490" t="s" s="2">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B490" t="s" s="2">
         <v>523</v>
@@ -62132,7 +62144,7 @@
     </row>
     <row r="491" hidden="true">
       <c r="A491" t="s" s="2">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B491" t="s" s="2">
         <v>528</v>
@@ -62249,7 +62261,7 @@
     </row>
     <row r="492" hidden="true">
       <c r="A492" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B492" t="s" s="2">
         <v>534</v>
@@ -62368,7 +62380,7 @@
     </row>
     <row r="493" hidden="true">
       <c r="A493" t="s" s="2">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B493" t="s" s="2">
         <v>542</v>
@@ -62487,7 +62499,7 @@
     </row>
     <row r="494" hidden="true">
       <c r="A494" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B494" t="s" s="2">
         <v>550</v>
@@ -62513,7 +62525,7 @@
         <v>19</v>
       </c>
       <c r="K494" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L494" t="s" s="2">
         <v>551</v>
@@ -62604,7 +62616,7 @@
     </row>
     <row r="495" hidden="true">
       <c r="A495" t="s" s="2">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B495" t="s" s="2">
         <v>557</v>
@@ -62723,7 +62735,7 @@
     </row>
     <row r="496" hidden="true">
       <c r="A496" t="s" s="2">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B496" t="s" s="2">
         <v>565</v>
@@ -62840,13 +62852,13 @@
     </row>
     <row r="497" hidden="true">
       <c r="A497" t="s" s="2">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B497" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D497" t="s" s="2">
         <v>19</v>
@@ -62871,10 +62883,10 @@
         <v>395</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="N497" s="2"/>
       <c r="O497" s="2"/>
@@ -62957,7 +62969,7 @@
     </row>
     <row r="498" hidden="true">
       <c r="A498" t="s" s="2">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B498" t="s" s="2">
         <v>503</v>
@@ -63072,7 +63084,7 @@
     </row>
     <row r="499" hidden="true">
       <c r="A499" t="s" s="2">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B499" t="s" s="2">
         <v>504</v>
@@ -63189,7 +63201,7 @@
     </row>
     <row r="500" hidden="true">
       <c r="A500" t="s" s="2">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B500" t="s" s="2">
         <v>505</v>
@@ -63308,7 +63320,7 @@
     </row>
     <row r="501" hidden="true">
       <c r="A501" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B501" t="s" s="2">
         <v>506</v>
@@ -63427,7 +63439,7 @@
     </row>
     <row r="502" hidden="true">
       <c r="A502" t="s" s="2">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B502" t="s" s="2">
         <v>512</v>
@@ -63475,7 +63487,7 @@
         <v>19</v>
       </c>
       <c r="S502" t="s" s="2">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="T502" t="s" s="2">
         <v>19</v>
@@ -63546,7 +63558,7 @@
     </row>
     <row r="503" hidden="true">
       <c r="A503" t="s" s="2">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B503" t="s" s="2">
         <v>519</v>
@@ -63663,7 +63675,7 @@
     </row>
     <row r="504" hidden="true">
       <c r="A504" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B504" t="s" s="2">
         <v>523</v>
@@ -63780,7 +63792,7 @@
     </row>
     <row r="505" hidden="true">
       <c r="A505" t="s" s="2">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B505" t="s" s="2">
         <v>528</v>
@@ -63897,7 +63909,7 @@
     </row>
     <row r="506" hidden="true">
       <c r="A506" t="s" s="2">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B506" t="s" s="2">
         <v>534</v>
@@ -64016,7 +64028,7 @@
     </row>
     <row r="507" hidden="true">
       <c r="A507" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B507" t="s" s="2">
         <v>542</v>
@@ -64135,7 +64147,7 @@
     </row>
     <row r="508" hidden="true">
       <c r="A508" t="s" s="2">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B508" t="s" s="2">
         <v>550</v>
@@ -64161,7 +64173,7 @@
         <v>19</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L508" t="s" s="2">
         <v>551</v>
@@ -64252,7 +64264,7 @@
     </row>
     <row r="509" hidden="true">
       <c r="A509" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B509" t="s" s="2">
         <v>557</v>
@@ -64371,7 +64383,7 @@
     </row>
     <row r="510" hidden="true">
       <c r="A510" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B510" t="s" s="2">
         <v>565</v>
@@ -64488,13 +64500,13 @@
     </row>
     <row r="511" hidden="true">
       <c r="A511" t="s" s="2">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B511" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D511" t="s" s="2">
         <v>19</v>
@@ -64519,10 +64531,10 @@
         <v>395</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="N511" s="2"/>
       <c r="O511" s="2"/>
@@ -64605,7 +64617,7 @@
     </row>
     <row r="512" hidden="true">
       <c r="A512" t="s" s="2">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B512" t="s" s="2">
         <v>503</v>
@@ -64720,7 +64732,7 @@
     </row>
     <row r="513" hidden="true">
       <c r="A513" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B513" t="s" s="2">
         <v>504</v>
@@ -64837,7 +64849,7 @@
     </row>
     <row r="514" hidden="true">
       <c r="A514" t="s" s="2">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B514" t="s" s="2">
         <v>505</v>
@@ -64956,7 +64968,7 @@
     </row>
     <row r="515" hidden="true">
       <c r="A515" t="s" s="2">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B515" t="s" s="2">
         <v>506</v>
@@ -65075,7 +65087,7 @@
     </row>
     <row r="516" hidden="true">
       <c r="A516" t="s" s="2">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B516" t="s" s="2">
         <v>512</v>
@@ -65123,7 +65135,7 @@
         <v>19</v>
       </c>
       <c r="S516" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="T516" t="s" s="2">
         <v>19</v>
@@ -65194,7 +65206,7 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>519</v>
@@ -65311,7 +65323,7 @@
     </row>
     <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B518" t="s" s="2">
         <v>523</v>
@@ -65428,7 +65440,7 @@
     </row>
     <row r="519" hidden="true">
       <c r="A519" t="s" s="2">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>528</v>
@@ -65545,7 +65557,7 @@
     </row>
     <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>534</v>
@@ -65664,7 +65676,7 @@
     </row>
     <row r="521" hidden="true">
       <c r="A521" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B521" t="s" s="2">
         <v>542</v>
@@ -65783,7 +65795,7 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B522" t="s" s="2">
         <v>550</v>
@@ -65809,7 +65821,7 @@
         <v>19</v>
       </c>
       <c r="K522" t="s" s="2">
-        <v>1142</v>
+        <v>1181</v>
       </c>
       <c r="L522" t="s" s="2">
         <v>551</v>
@@ -65900,7 +65912,7 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>557</v>
@@ -66019,7 +66031,7 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>565</v>
@@ -66136,13 +66148,13 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B525" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="D525" t="s" s="2">
         <v>19</v>
@@ -66167,10 +66179,10 @@
         <v>395</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="N525" s="2"/>
       <c r="O525" s="2"/>
@@ -66253,7 +66265,7 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B526" t="s" s="2">
         <v>503</v>
@@ -66368,7 +66380,7 @@
     </row>
     <row r="527" hidden="true">
       <c r="A527" t="s" s="2">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="B527" t="s" s="2">
         <v>504</v>
@@ -66485,7 +66497,7 @@
     </row>
     <row r="528" hidden="true">
       <c r="A528" t="s" s="2">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="B528" t="s" s="2">
         <v>505</v>
@@ -66604,7 +66616,7 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="B529" t="s" s="2">
         <v>506</v>
@@ -66723,7 +66735,7 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B530" t="s" s="2">
         <v>512</v>
@@ -66771,7 +66783,7 @@
         <v>19</v>
       </c>
       <c r="S530" t="s" s="2">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="T530" t="s" s="2">
         <v>19</v>
@@ -66842,7 +66854,7 @@
     </row>
     <row r="531" hidden="true">
       <c r="A531" t="s" s="2">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="B531" t="s" s="2">
         <v>519</v>
@@ -66959,7 +66971,7 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B532" t="s" s="2">
         <v>523</v>
@@ -67076,7 +67088,7 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="B533" t="s" s="2">
         <v>528</v>
@@ -67193,7 +67205,7 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>534</v>
@@ -67312,7 +67324,7 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>542</v>
@@ -67431,7 +67443,7 @@
     </row>
     <row r="536" hidden="true">
       <c r="A536" t="s" s="2">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="B536" t="s" s="2">
         <v>550</v>
@@ -67457,7 +67469,7 @@
         <v>19</v>
       </c>
       <c r="K536" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L536" t="s" s="2">
         <v>551</v>
@@ -67548,7 +67560,7 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="B537" t="s" s="2">
         <v>557</v>
@@ -67667,7 +67679,7 @@
     </row>
     <row r="538" hidden="true">
       <c r="A538" t="s" s="2">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="B538" t="s" s="2">
         <v>565</v>
@@ -67784,13 +67796,13 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="B539" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D539" t="s" s="2">
         <v>19</v>
@@ -67815,10 +67827,10 @@
         <v>395</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="N539" s="2"/>
       <c r="O539" s="2"/>
@@ -67901,7 +67913,7 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>503</v>
@@ -68016,7 +68028,7 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>504</v>
@@ -68133,7 +68145,7 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>505</v>
@@ -68252,7 +68264,7 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>506</v>
@@ -68371,7 +68383,7 @@
     </row>
     <row r="544" hidden="true">
       <c r="A544" t="s" s="2">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>512</v>
@@ -68419,7 +68431,7 @@
         <v>19</v>
       </c>
       <c r="S544" t="s" s="2">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="T544" t="s" s="2">
         <v>19</v>
@@ -68490,7 +68502,7 @@
     </row>
     <row r="545" hidden="true">
       <c r="A545" t="s" s="2">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B545" t="s" s="2">
         <v>519</v>
@@ -68607,7 +68619,7 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B546" t="s" s="2">
         <v>523</v>
@@ -68724,7 +68736,7 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="B547" t="s" s="2">
         <v>528</v>
@@ -68841,7 +68853,7 @@
     </row>
     <row r="548" hidden="true">
       <c r="A548" t="s" s="2">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B548" t="s" s="2">
         <v>534</v>
@@ -68960,7 +68972,7 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>542</v>
@@ -69079,7 +69091,7 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="B550" t="s" s="2">
         <v>550</v>
@@ -69196,7 +69208,7 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>557</v>
@@ -69315,7 +69327,7 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B552" t="s" s="2">
         <v>565</v>
@@ -69432,13 +69444,13 @@
     </row>
     <row r="553" hidden="true">
       <c r="A553" t="s" s="2">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="D553" t="s" s="2">
         <v>19</v>
@@ -69463,10 +69475,10 @@
         <v>395</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="N553" s="2"/>
       <c r="O553" s="2"/>
@@ -69549,7 +69561,7 @@
     </row>
     <row r="554" hidden="true">
       <c r="A554" t="s" s="2">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B554" t="s" s="2">
         <v>503</v>
@@ -69664,7 +69676,7 @@
     </row>
     <row r="555" hidden="true">
       <c r="A555" t="s" s="2">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B555" t="s" s="2">
         <v>504</v>
@@ -69781,7 +69793,7 @@
     </row>
     <row r="556" hidden="true">
       <c r="A556" t="s" s="2">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B556" t="s" s="2">
         <v>505</v>
@@ -69900,7 +69912,7 @@
     </row>
     <row r="557" hidden="true">
       <c r="A557" t="s" s="2">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B557" t="s" s="2">
         <v>506</v>
@@ -70019,7 +70031,7 @@
     </row>
     <row r="558" hidden="true">
       <c r="A558" t="s" s="2">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B558" t="s" s="2">
         <v>512</v>
@@ -70067,7 +70079,7 @@
         <v>19</v>
       </c>
       <c r="S558" t="s" s="2">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="T558" t="s" s="2">
         <v>19</v>
@@ -70138,7 +70150,7 @@
     </row>
     <row r="559" hidden="true">
       <c r="A559" t="s" s="2">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>519</v>
@@ -70255,7 +70267,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>523</v>
@@ -70372,7 +70384,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>528</v>
@@ -70489,7 +70501,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>534</v>
@@ -70608,7 +70620,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>542</v>
@@ -70727,7 +70739,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>550</v>
@@ -70753,7 +70765,7 @@
         <v>19</v>
       </c>
       <c r="K564" t="s" s="2">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="L564" t="s" s="2">
         <v>551</v>
@@ -70844,7 +70856,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>557</v>
@@ -70963,7 +70975,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>565</v>
@@ -71080,13 +71092,13 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D567" t="s" s="2">
         <v>19</v>
@@ -71111,10 +71123,10 @@
         <v>395</v>
       </c>
       <c r="L567" t="s" s="2">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="M567" t="s" s="2">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="N567" s="2"/>
       <c r="O567" s="2"/>
@@ -71197,7 +71209,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>503</v>
@@ -71312,7 +71324,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>504</v>
@@ -71429,7 +71441,7 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>505</v>
@@ -71548,7 +71560,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>506</v>
@@ -71667,7 +71679,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>512</v>
@@ -71715,7 +71727,7 @@
         <v>19</v>
       </c>
       <c r="S572" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="T572" t="s" s="2">
         <v>19</v>
@@ -71786,7 +71798,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>519</v>
@@ -71903,7 +71915,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>523</v>
@@ -72020,7 +72032,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>528</v>
@@ -72137,7 +72149,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>534</v>
@@ -72256,7 +72268,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>542</v>
@@ -72375,7 +72387,7 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>550</v>
@@ -72404,10 +72416,10 @@
         <v>491</v>
       </c>
       <c r="L578" t="s" s="2">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="M578" t="s" s="2">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="N578" t="s" s="2">
         <v>553</v>
@@ -72448,7 +72460,7 @@
         <v>19</v>
       </c>
       <c r="AB578" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AC578" s="2"/>
       <c r="AD578" t="s" s="2">
@@ -72490,13 +72502,13 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="D579" t="s" s="2">
         <v>19</v>
@@ -72518,13 +72530,13 @@
         <v>19</v>
       </c>
       <c r="K579" t="s" s="2">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="L579" t="s" s="2">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="M579" t="s" s="2">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="N579" t="s" s="2">
         <v>553</v>
@@ -72609,7 +72621,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>557</v>
@@ -72728,7 +72740,7 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>565</v>
@@ -72845,13 +72857,13 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>495</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D582" t="s" s="2">
         <v>19</v>
@@ -72876,10 +72888,10 @@
         <v>395</v>
       </c>
       <c r="L582" t="s" s="2">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="M582" t="s" s="2">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="N582" s="2"/>
       <c r="O582" s="2"/>
@@ -72962,7 +72974,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>503</v>
@@ -73077,7 +73089,7 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B584" t="s" s="2">
         <v>504</v>
@@ -73194,7 +73206,7 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B585" t="s" s="2">
         <v>505</v>
@@ -73313,7 +73325,7 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B586" t="s" s="2">
         <v>506</v>
@@ -73432,7 +73444,7 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B587" t="s" s="2">
         <v>512</v>
@@ -73480,7 +73492,7 @@
         <v>19</v>
       </c>
       <c r="S587" t="s" s="2">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="T587" t="s" s="2">
         <v>19</v>
@@ -73551,7 +73563,7 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B588" t="s" s="2">
         <v>519</v>
@@ -73668,7 +73680,7 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B589" t="s" s="2">
         <v>523</v>
@@ -73785,7 +73797,7 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B590" t="s" s="2">
         <v>528</v>
@@ -73902,7 +73914,7 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B591" t="s" s="2">
         <v>534</v>
@@ -74021,7 +74033,7 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B592" t="s" s="2">
         <v>542</v>
@@ -74140,7 +74152,7 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B593" t="s" s="2">
         <v>550</v>
@@ -74166,7 +74178,7 @@
         <v>19</v>
       </c>
       <c r="K593" t="s" s="2">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="L593" t="s" s="2">
         <v>551</v>
@@ -74257,7 +74269,7 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="B594" t="s" s="2">
         <v>557</v>
@@ -74376,7 +74388,7 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B595" t="s" s="2">
         <v>565</v>

--- a/StructureDefinition-VunsPneumoComposition.xlsx
+++ b/StructureDefinition-VunsPneumoComposition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
